--- a/CRM - AOI Beta Demo.xlsx
+++ b/CRM - AOI Beta Demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22365" windowHeight="18150" activeTab="4"/>
+    <workbookView windowWidth="22365" windowHeight="18150" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Location" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="38">
   <si>
     <t>WELL</t>
   </si>
@@ -19990,7 +19990,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF94"/>
+  <dimension ref="A1:X94"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.8166666666667" customWidth="1"/>
@@ -20005,7 +20005,7 @@
     <col min="14" max="14" width="9.725" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>33</v>
       </c>
@@ -20077,30 +20077,6 @@
       </c>
       <c r="X1" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:24">
@@ -24421,7 +24397,7 @@
         <v>0.958881728593385</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1e-5</v>
       </c>
       <c r="J60">
         <v>0.873547821089084</v>
